--- a/Data Files/Driver_Experience.xlsx
+++ b/Data Files/Driver_Experience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D99F85-A516-40F6-99C3-99FFD4097913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA939B10-0F36-4200-8DE0-3BA5D0736780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" activeTab="7" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="1993" sheetId="5" r:id="rId4"/>
     <sheet name="1994" sheetId="6" r:id="rId5"/>
     <sheet name="1995" sheetId="7" r:id="rId6"/>
-    <sheet name="1997" sheetId="9" r:id="rId7"/>
-    <sheet name="1996" sheetId="8" r:id="rId8"/>
+    <sheet name="1996" sheetId="8" r:id="rId7"/>
+    <sheet name="1997" sheetId="9" r:id="rId8"/>
     <sheet name="1998" sheetId="10" r:id="rId9"/>
     <sheet name="1999" sheetId="11" r:id="rId10"/>
     <sheet name="2000" sheetId="12" r:id="rId11"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="152">
   <si>
     <t>Driver</t>
   </si>
@@ -522,9 +522,6 @@
   </si>
   <si>
     <t>Arvid Lindblad</t>
-  </si>
-  <si>
-    <t>.</t>
   </si>
   <si>
     <t>Luca Badoer</t>
@@ -1017,10 +1014,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1602,170 +1598,176 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AK126"/>
+  <dimension ref="A1:AL126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="C1">
         <v>2026</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2025</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2024</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2023</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2022</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2021</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2020</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2019</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2018</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2017</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2016</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2015</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2014</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2013</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2012</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2011</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2010</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2009</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2008</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2007</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2006</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2005</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2004</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2003</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2002</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2001</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2000</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>1999</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>1998</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>1997</v>
       </c>
-      <c r="AF1">
+      <c r="AG1">
         <v>1996</v>
       </c>
-      <c r="AG1">
+      <c r="AH1">
         <v>1995</v>
       </c>
-      <c r="AH1">
+      <c r="AI1">
         <v>1994</v>
       </c>
-      <c r="AI1">
+      <c r="AJ1">
         <v>1993</v>
       </c>
-      <c r="AJ1">
+      <c r="AK1">
         <v>1992</v>
       </c>
-      <c r="AK1">
+      <c r="AL1">
         <v>1991</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
         <v>17</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>12</v>
-      </c>
-      <c r="AI2">
-        <v>16</v>
       </c>
       <c r="AJ2">
         <v>16</v>
       </c>
       <c r="AK2">
+        <v>16</v>
+      </c>
+      <c r="AL2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
         <v>17</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>15</v>
       </c>
-      <c r="AI3">
+      <c r="AJ3">
         <v>14</v>
       </c>
-      <c r="AJ3" s="1">
-        <v>0</v>
-      </c>
       <c r="AK3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
@@ -1785,32 +1787,37 @@
       <c r="AK4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="AG5">
+        <v>16</v>
+      </c>
+      <c r="AH5">
         <v>17</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>8</v>
       </c>
-      <c r="AI5" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ5" s="1">
         <v>0</v>
       </c>
       <c r="AK5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
@@ -1830,12 +1837,14 @@
       <c r="AK6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="AF7" s="1"/>
       <c r="AG7" s="1">
         <v>0</v>
       </c>
@@ -1851,12 +1860,14 @@
       <c r="AK7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -1877,12 +1888,14 @@
       <c r="AK8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
@@ -1901,16 +1914,16 @@
       <c r="AK9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="Y10" t="s">
-        <v>151</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>0</v>
+      <c r="AG10">
+        <v>16</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1924,32 +1937,37 @@
       <c r="AK10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="AG11">
+        <v>16</v>
+      </c>
+      <c r="AH11">
         <v>17</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>15</v>
       </c>
-      <c r="AI11" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ11" s="1">
         <v>0</v>
       </c>
       <c r="AK11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
@@ -1968,12 +1986,14 @@
       <c r="AK12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="AF13" s="1"/>
       <c r="AG13" s="1">
         <v>0</v>
       </c>
@@ -1989,12 +2009,14 @@
       <c r="AK13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -2015,13 +2037,16 @@
       <c r="AK14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="AG15" s="1">
-        <v>0</v>
+      <c r="AG15">
+        <v>8</v>
       </c>
       <c r="AH15" s="1">
         <v>0</v>
@@ -2035,12 +2060,14 @@
       <c r="AK15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="AD16" s="1"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1">
@@ -2058,32 +2085,37 @@
       <c r="AK16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="AG17">
+        <v>16</v>
+      </c>
+      <c r="AH17">
         <v>17</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>12</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <v>2</v>
       </c>
-      <c r="AJ17" s="1">
-        <v>0</v>
-      </c>
       <c r="AK17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -2104,12 +2136,14 @@
       <c r="AK18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
@@ -2130,12 +2164,14 @@
       <c r="AK19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
@@ -2155,12 +2191,14 @@
       <c r="AK20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
@@ -2180,52 +2218,60 @@
       <c r="AK21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
       <c r="AG22">
+        <v>16</v>
+      </c>
+      <c r="AH22">
         <v>17</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>15</v>
       </c>
-      <c r="AI22" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ22" s="1">
         <v>0</v>
       </c>
       <c r="AK22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="AG23">
+        <v>15</v>
+      </c>
+      <c r="AH23">
         <v>17</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>2</v>
       </c>
-      <c r="AI23" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="1">
         <v>0</v>
       </c>
       <c r="AK23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
@@ -2246,12 +2292,14 @@
       <c r="AK24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
-      <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -2271,12 +2319,14 @@
       <c r="AK25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
@@ -2298,12 +2348,14 @@
       <c r="AK26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
@@ -2325,32 +2377,37 @@
       <c r="AK27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="AG28">
+        <v>16</v>
+      </c>
+      <c r="AH28">
         <v>5</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>10</v>
       </c>
-      <c r="AI28" s="1">
-        <v>0</v>
-      </c>
       <c r="AJ28" s="1">
         <v>0</v>
       </c>
       <c r="AK28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
@@ -2372,12 +2429,14 @@
       <c r="AK29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
-      <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
@@ -2399,12 +2458,14 @@
       <c r="AK30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
@@ -2424,12 +2485,14 @@
       <c r="AK31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>56</v>
       </c>
-      <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
@@ -2451,12 +2514,14 @@
       <c r="AK32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1">
@@ -2474,12 +2539,14 @@
       <c r="AK33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>57</v>
       </c>
-      <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -2501,12 +2568,14 @@
       <c r="AK34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>58</v>
       </c>
-      <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
@@ -2528,12 +2597,14 @@
       <c r="AK35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>59</v>
       </c>
-      <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
@@ -2555,12 +2626,14 @@
       <c r="AK36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>60</v>
       </c>
-      <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
@@ -2582,12 +2655,14 @@
       <c r="AK37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>61</v>
       </c>
-      <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
@@ -2609,12 +2684,14 @@
       <c r="AK38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>62</v>
       </c>
-      <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -2637,12 +2714,14 @@
       <c r="AK39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>63</v>
       </c>
-      <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
@@ -2665,12 +2744,14 @@
       <c r="AK40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>64</v>
       </c>
-      <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1">
@@ -2688,12 +2769,14 @@
       <c r="AK41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>65</v>
       </c>
-      <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
@@ -2716,12 +2799,14 @@
       <c r="AK42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>66</v>
       </c>
-      <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
@@ -2744,12 +2829,14 @@
       <c r="AK43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>67</v>
       </c>
-      <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
@@ -2773,12 +2860,14 @@
       <c r="AK44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
       </c>
-      <c r="AF45" s="1"/>
       <c r="AG45" s="1">
         <v>0</v>
       </c>
@@ -2794,12 +2883,14 @@
       <c r="AK45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>69</v>
       </c>
-      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
@@ -2823,12 +2914,14 @@
       <c r="AK46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>70</v>
       </c>
-      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
@@ -2852,12 +2945,14 @@
       <c r="AK47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>71</v>
       </c>
-      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
@@ -2881,12 +2976,14 @@
       <c r="AK48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>72</v>
       </c>
-      <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
@@ -2910,12 +3007,14 @@
       <c r="AK49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>73</v>
       </c>
-      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -2939,12 +3038,14 @@
       <c r="AK50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>74</v>
       </c>
-      <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
@@ -2969,12 +3070,14 @@
       <c r="AK51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>75</v>
       </c>
-      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
@@ -2999,12 +3102,14 @@
       <c r="AK52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>76</v>
       </c>
-      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
@@ -3029,12 +3134,14 @@
       <c r="AK53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>77</v>
       </c>
-      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
@@ -3059,12 +3166,14 @@
       <c r="AK54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>78</v>
       </c>
-      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
@@ -3089,12 +3198,14 @@
       <c r="AK55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>79</v>
       </c>
-      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
@@ -3119,12 +3230,14 @@
       <c r="AK56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>80</v>
       </c>
-      <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
@@ -3150,12 +3263,14 @@
       <c r="AK57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>81</v>
       </c>
-      <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
@@ -3181,12 +3296,14 @@
       <c r="AK58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>82</v>
       </c>
-      <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
@@ -3212,12 +3329,14 @@
       <c r="AK59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>83</v>
       </c>
-      <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -3243,12 +3362,14 @@
       <c r="AK60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>84</v>
       </c>
-      <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -3274,12 +3395,14 @@
       <c r="AK61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>86</v>
       </c>
-      <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
@@ -3306,12 +3429,14 @@
       <c r="AK62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>87</v>
       </c>
-      <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
@@ -3338,12 +3463,14 @@
       <c r="AK63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>88</v>
       </c>
-      <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
@@ -3371,12 +3498,14 @@
       <c r="AK64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>89</v>
       </c>
-      <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
@@ -3404,12 +3533,14 @@
       <c r="AK65" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>90</v>
       </c>
-      <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
@@ -3437,12 +3568,14 @@
       <c r="AK66" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>91</v>
       </c>
-      <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -3470,46 +3603,37 @@
       <c r="AK67" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>92</v>
       </c>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-      <c r="W68" s="2"/>
-      <c r="X68" s="2"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="2"/>
-      <c r="AA68" s="2"/>
-      <c r="AB68" s="2"/>
-      <c r="AC68" s="2"/>
-      <c r="AD68" s="2"/>
-      <c r="AE68" s="2"/>
-      <c r="AF68" s="2"/>
-      <c r="AG68" s="2">
+      <c r="AG68">
+        <v>6</v>
+      </c>
+      <c r="AH68">
         <v>15</v>
       </c>
-      <c r="AH68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI68" s="2">
+      <c r="AI68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ68">
         <v>12</v>
       </c>
-      <c r="AJ68" s="1">
-        <v>0</v>
-      </c>
       <c r="AK68" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>93</v>
       </c>
-      <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
@@ -3538,12 +3662,14 @@
       <c r="AK69" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>94</v>
       </c>
-      <c r="S70" s="1"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
@@ -3572,12 +3698,14 @@
       <c r="AK70" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>95</v>
       </c>
-      <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
@@ -3606,12 +3734,14 @@
       <c r="AK71" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>96</v>
       </c>
-      <c r="S72" s="1"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
@@ -3640,12 +3770,14 @@
       <c r="AK72" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>97</v>
       </c>
-      <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
@@ -3674,12 +3806,14 @@
       <c r="AK73" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>98</v>
       </c>
-      <c r="R74" s="1"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
@@ -3709,12 +3843,14 @@
       <c r="AK74" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>99</v>
       </c>
-      <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -3744,12 +3880,14 @@
       <c r="AK75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>100</v>
       </c>
-      <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -3779,12 +3917,14 @@
       <c r="AK76" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>101</v>
       </c>
-      <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -3814,12 +3954,14 @@
       <c r="AK77" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>102</v>
       </c>
-      <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -3849,12 +3991,14 @@
       <c r="AK78" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>103</v>
       </c>
-      <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
@@ -3885,12 +4029,14 @@
       <c r="AK79" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>104</v>
       </c>
-      <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
@@ -3921,12 +4067,14 @@
       <c r="AK80" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>105</v>
       </c>
-      <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -3958,12 +4106,14 @@
       <c r="AK81" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>106</v>
       </c>
-      <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -3995,12 +4145,14 @@
       <c r="AK82" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>107</v>
       </c>
-      <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -4032,12 +4184,14 @@
       <c r="AK83" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL83" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>108</v>
       </c>
-      <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -4069,12 +4223,14 @@
       <c r="AK84" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>109</v>
       </c>
-      <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -4106,12 +4262,14 @@
       <c r="AK85" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>110</v>
       </c>
-      <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
@@ -4144,12 +4302,14 @@
       <c r="AK86" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>111</v>
       </c>
-      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
@@ -4182,12 +4342,14 @@
       <c r="AK87" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>112</v>
       </c>
-      <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
@@ -4220,12 +4382,14 @@
       <c r="AK88" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>113</v>
       </c>
-      <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
@@ -4258,12 +4422,14 @@
       <c r="AK89" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>114</v>
       </c>
-      <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -4297,12 +4463,14 @@
       <c r="AK90" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>115</v>
       </c>
-      <c r="N91" s="1"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
@@ -4336,12 +4504,14 @@
       <c r="AK91" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>116</v>
       </c>
-      <c r="N92" s="1"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -4375,12 +4545,14 @@
       <c r="AK92" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>117</v>
       </c>
-      <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
@@ -4414,12 +4586,14 @@
       <c r="AK93" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>118</v>
       </c>
-      <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
@@ -4453,12 +4627,14 @@
       <c r="AK94" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL94" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>119</v>
       </c>
-      <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
@@ -4493,12 +4669,14 @@
       <c r="AK95" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL95" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>120</v>
       </c>
-      <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
@@ -4533,12 +4711,14 @@
       <c r="AK96" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL96" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>121</v>
       </c>
-      <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
@@ -4573,12 +4753,14 @@
       <c r="AK97" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>122</v>
       </c>
-      <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
@@ -4613,12 +4795,14 @@
       <c r="AK98" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>123</v>
       </c>
-      <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
@@ -4653,12 +4837,14 @@
       <c r="AK99" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>124</v>
       </c>
-      <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
@@ -4694,12 +4880,14 @@
       <c r="AK100" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>125</v>
       </c>
-      <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -4735,12 +4923,14 @@
       <c r="AK101" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>126</v>
       </c>
-      <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -4776,12 +4966,14 @@
       <c r="AK102" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>127</v>
       </c>
-      <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -4817,12 +5009,14 @@
       <c r="AK103" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>128</v>
       </c>
-      <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -4859,12 +5053,14 @@
       <c r="AK104" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>129</v>
       </c>
-      <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -4901,12 +5097,14 @@
       <c r="AK105" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL105" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>130</v>
       </c>
-      <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -4944,12 +5142,14 @@
       <c r="AK106" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL106" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>131</v>
       </c>
-      <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -4987,12 +5187,14 @@
       <c r="AK107" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL107" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>132</v>
       </c>
-      <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -5030,12 +5232,14 @@
       <c r="AK108" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL108" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>133</v>
       </c>
-      <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -5074,12 +5278,14 @@
       <c r="AK109" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>134</v>
       </c>
-      <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -5118,12 +5324,14 @@
       <c r="AK110" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>135</v>
       </c>
-      <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -5162,12 +5370,14 @@
       <c r="AK111" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>136</v>
       </c>
-      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
@@ -5207,12 +5417,14 @@
       <c r="AK112" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>137</v>
       </c>
-      <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -5252,12 +5464,14 @@
       <c r="AK113" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>138</v>
       </c>
-      <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -5297,12 +5511,14 @@
       <c r="AK114" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>139</v>
       </c>
-      <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -5343,12 +5559,14 @@
       <c r="AK115" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>140</v>
       </c>
-      <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -5389,12 +5607,14 @@
       <c r="AK116" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>141</v>
       </c>
-      <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -5436,12 +5656,14 @@
       <c r="AK117" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>142</v>
       </c>
-      <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -5483,12 +5705,14 @@
       <c r="AK118" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>143</v>
       </c>
-      <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -5530,12 +5754,14 @@
       <c r="AK119" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>144</v>
       </c>
-      <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -5578,12 +5804,14 @@
       <c r="AK120" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>145</v>
       </c>
-      <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -5626,12 +5854,14 @@
       <c r="AK121" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL121" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>146</v>
       </c>
-      <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -5674,12 +5904,14 @@
       <c r="AK122" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>147</v>
       </c>
-      <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -5723,12 +5955,14 @@
       <c r="AK123" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>148</v>
       </c>
-      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -5772,12 +6006,14 @@
       <c r="AK124" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>149</v>
       </c>
-      <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -5821,12 +6057,14 @@
       <c r="AK125" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>150</v>
       </c>
-      <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -5871,6 +6109,9 @@
       <c r="AK126" s="1">
         <v>0</v>
       </c>
+      <c r="AL126" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11095,7 +11336,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -11159,21 +11400,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11241,55 +11467,642 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B12" si="0">SUM(C3:R3)</f>
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>92</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/Driver_Experience.xlsx
+++ b/Data Files/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA939B10-0F36-4200-8DE0-3BA5D0736780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947D4AC7-C7C1-46C0-B993-65F44F0EA1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>Luca Badoer</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
   </si>
 </sst>
 </file>
@@ -1722,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AF2">
+        <v>17</v>
+      </c>
       <c r="AG2">
         <v>15</v>
       </c>
@@ -1745,6 +1751,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AF3">
+        <v>17</v>
+      </c>
       <c r="AG3">
         <v>16</v>
       </c>
@@ -1771,7 +1780,9 @@
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
+      <c r="AF4" s="1">
+        <v>0</v>
+      </c>
       <c r="AG4" s="1">
         <v>0</v>
       </c>
@@ -1795,6 +1806,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AF5">
+        <v>17</v>
+      </c>
       <c r="AG5">
         <v>16</v>
       </c>
@@ -1821,7 +1835,9 @@
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
+      <c r="AF6" s="1">
+        <v>0</v>
+      </c>
       <c r="AG6" s="1">
         <v>0</v>
       </c>
@@ -1844,6 +1860,9 @@
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
+      </c>
+      <c r="AF7">
+        <v>17</v>
       </c>
       <c r="AG7" s="1">
         <v>0</v>
@@ -1872,7 +1891,9 @@
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
+      <c r="AF8" s="1">
+        <v>0</v>
+      </c>
       <c r="AG8" s="1">
         <v>0</v>
       </c>
@@ -1898,7 +1919,9 @@
       </c>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
+      <c r="AF9" s="1">
+        <v>0</v>
+      </c>
       <c r="AG9" s="1">
         <v>0</v>
       </c>
@@ -1922,6 +1945,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AF10">
+        <v>16</v>
+      </c>
       <c r="AG10">
         <v>16</v>
       </c>
@@ -1945,6 +1971,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AF11">
+        <v>10</v>
+      </c>
       <c r="AG11">
         <v>16</v>
       </c>
@@ -1970,7 +1999,9 @@
       </c>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
+      <c r="AF12" s="1">
+        <v>0</v>
+      </c>
       <c r="AG12" s="1">
         <v>0</v>
       </c>
@@ -1993,6 +2024,9 @@
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
+      </c>
+      <c r="AF13">
+        <v>13</v>
       </c>
       <c r="AG13" s="1">
         <v>0</v>
@@ -2021,7 +2055,9 @@
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
+      <c r="AF14" s="1">
+        <v>0</v>
+      </c>
       <c r="AG14" s="1">
         <v>0</v>
       </c>
@@ -2045,6 +2081,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AF15">
+        <v>17</v>
+      </c>
       <c r="AG15">
         <v>8</v>
       </c>
@@ -2069,7 +2108,9 @@
         <v>15</v>
       </c>
       <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
+      <c r="AF16" s="1">
+        <v>0</v>
+      </c>
       <c r="AG16" s="1">
         <v>0</v>
       </c>
@@ -2092,6 +2133,9 @@
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
+      </c>
+      <c r="AF17">
+        <v>17</v>
       </c>
       <c r="AG17">
         <v>16</v>
@@ -2120,7 +2164,9 @@
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
+      <c r="AF18" s="1">
+        <v>0</v>
+      </c>
       <c r="AG18" s="1">
         <v>0</v>
       </c>
@@ -2226,6 +2272,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AF22">
+        <v>17</v>
+      </c>
       <c r="AG22">
         <v>16</v>
       </c>
@@ -2248,6 +2297,9 @@
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
+      </c>
+      <c r="AF23">
+        <v>17</v>
       </c>
       <c r="AG23">
         <v>15</v>
@@ -2276,7 +2328,9 @@
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
+      <c r="AF24" s="1">
+        <v>0</v>
+      </c>
       <c r="AG24" s="1">
         <v>0</v>
       </c>
@@ -2385,6 +2439,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AF28">
+        <v>17</v>
+      </c>
       <c r="AG28">
         <v>16</v>
       </c>
@@ -2413,7 +2470,9 @@
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
-      <c r="AF29" s="1"/>
+      <c r="AF29" s="1">
+        <v>0</v>
+      </c>
       <c r="AG29" s="1">
         <v>0</v>
       </c>
@@ -2442,7 +2501,9 @@
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
+      <c r="AF30" s="1">
+        <v>0</v>
+      </c>
       <c r="AG30" s="1">
         <v>0</v>
       </c>
@@ -2469,7 +2530,9 @@
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
-      <c r="AF31" s="1"/>
+      <c r="AF31" s="1">
+        <v>0</v>
+      </c>
       <c r="AG31" s="1">
         <v>0</v>
       </c>
@@ -2498,7 +2561,9 @@
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
-      <c r="AF32" s="1"/>
+      <c r="AF32" s="1">
+        <v>0</v>
+      </c>
       <c r="AG32" s="1">
         <v>0</v>
       </c>
@@ -2523,7 +2588,9 @@
         <v>53</v>
       </c>
       <c r="AE33" s="1"/>
-      <c r="AF33" s="1"/>
+      <c r="AF33" s="1">
+        <v>0</v>
+      </c>
       <c r="AG33" s="1">
         <v>0</v>
       </c>
@@ -2552,7 +2619,9 @@
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
-      <c r="AF34" s="1"/>
+      <c r="AF34" s="1">
+        <v>0</v>
+      </c>
       <c r="AG34" s="1">
         <v>0</v>
       </c>
@@ -2581,7 +2650,9 @@
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
-      <c r="AF35" s="1"/>
+      <c r="AF35" s="1">
+        <v>0</v>
+      </c>
       <c r="AG35" s="1">
         <v>0</v>
       </c>
@@ -2610,7 +2681,9 @@
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
-      <c r="AF36" s="1"/>
+      <c r="AF36" s="1">
+        <v>0</v>
+      </c>
       <c r="AG36" s="1">
         <v>0</v>
       </c>
@@ -2639,7 +2712,9 @@
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
+      <c r="AF37" s="1">
+        <v>0</v>
+      </c>
       <c r="AG37" s="1">
         <v>0</v>
       </c>
@@ -2668,7 +2743,9 @@
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
-      <c r="AF38" s="1"/>
+      <c r="AF38" s="1">
+        <v>0</v>
+      </c>
       <c r="AG38" s="1">
         <v>0</v>
       </c>
@@ -2698,7 +2775,9 @@
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
-      <c r="AF39" s="1"/>
+      <c r="AF39" s="1">
+        <v>0</v>
+      </c>
       <c r="AG39" s="1">
         <v>0</v>
       </c>
@@ -2728,7 +2807,9 @@
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
-      <c r="AF40" s="1"/>
+      <c r="AF40" s="1">
+        <v>0</v>
+      </c>
       <c r="AG40" s="1">
         <v>0</v>
       </c>
@@ -2753,7 +2834,9 @@
         <v>64</v>
       </c>
       <c r="AE41" s="1"/>
-      <c r="AF41" s="1"/>
+      <c r="AF41" s="1">
+        <v>0</v>
+      </c>
       <c r="AG41" s="1">
         <v>0</v>
       </c>
@@ -2783,7 +2866,9 @@
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
-      <c r="AF42" s="1"/>
+      <c r="AF42" s="1">
+        <v>0</v>
+      </c>
       <c r="AG42" s="1">
         <v>0</v>
       </c>
@@ -2813,7 +2898,9 @@
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
-      <c r="AF43" s="1"/>
+      <c r="AF43" s="1">
+        <v>0</v>
+      </c>
       <c r="AG43" s="1">
         <v>0</v>
       </c>
@@ -2844,7 +2931,9 @@
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
-      <c r="AF44" s="1"/>
+      <c r="AF44" s="1">
+        <v>0</v>
+      </c>
       <c r="AG44" s="1">
         <v>0</v>
       </c>
@@ -2867,6 +2956,9 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AF45">
+        <v>3</v>
       </c>
       <c r="AG45" s="1">
         <v>0</v>
@@ -2898,7 +2990,9 @@
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
-      <c r="AF46" s="1"/>
+      <c r="AF46" s="1">
+        <v>0</v>
+      </c>
       <c r="AG46" s="1">
         <v>0</v>
       </c>
@@ -2929,7 +3023,9 @@
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
-      <c r="AF47" s="1"/>
+      <c r="AF47" s="1">
+        <v>0</v>
+      </c>
       <c r="AG47" s="1">
         <v>0</v>
       </c>
@@ -2960,7 +3056,9 @@
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
-      <c r="AF48" s="1"/>
+      <c r="AF48" s="1">
+        <v>0</v>
+      </c>
       <c r="AG48" s="1">
         <v>0</v>
       </c>
@@ -2991,7 +3089,9 @@
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
-      <c r="AF49" s="1"/>
+      <c r="AF49" s="1">
+        <v>0</v>
+      </c>
       <c r="AG49" s="1">
         <v>0</v>
       </c>
@@ -3022,7 +3122,9 @@
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
-      <c r="AF50" s="1"/>
+      <c r="AF50" s="1">
+        <v>0</v>
+      </c>
       <c r="AG50" s="1">
         <v>0</v>
       </c>
@@ -3054,7 +3156,9 @@
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
-      <c r="AF51" s="1"/>
+      <c r="AF51" s="1">
+        <v>0</v>
+      </c>
       <c r="AG51" s="1">
         <v>0</v>
       </c>
@@ -3086,7 +3190,9 @@
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
-      <c r="AF52" s="1"/>
+      <c r="AF52" s="1">
+        <v>0</v>
+      </c>
       <c r="AG52" s="1">
         <v>0</v>
       </c>
@@ -3118,7 +3224,9 @@
       <c r="AC53" s="1"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
-      <c r="AF53" s="1"/>
+      <c r="AF53" s="1">
+        <v>0</v>
+      </c>
       <c r="AG53" s="1">
         <v>0</v>
       </c>
@@ -3150,7 +3258,9 @@
       <c r="AC54" s="1"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
-      <c r="AF54" s="1"/>
+      <c r="AF54" s="1">
+        <v>0</v>
+      </c>
       <c r="AG54" s="1">
         <v>0</v>
       </c>
@@ -3182,7 +3292,9 @@
       <c r="AC55" s="1"/>
       <c r="AD55" s="1"/>
       <c r="AE55" s="1"/>
-      <c r="AF55" s="1"/>
+      <c r="AF55" s="1">
+        <v>0</v>
+      </c>
       <c r="AG55" s="1">
         <v>0</v>
       </c>
@@ -3214,7 +3326,9 @@
       <c r="AC56" s="1"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
-      <c r="AF56" s="1"/>
+      <c r="AF56" s="1">
+        <v>0</v>
+      </c>
       <c r="AG56" s="1">
         <v>0</v>
       </c>
@@ -3247,7 +3361,9 @@
       <c r="AC57" s="1"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
-      <c r="AF57" s="1"/>
+      <c r="AF57" s="1">
+        <v>0</v>
+      </c>
       <c r="AG57" s="1">
         <v>0</v>
       </c>
@@ -3280,7 +3396,9 @@
       <c r="AC58" s="1"/>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1"/>
-      <c r="AF58" s="1"/>
+      <c r="AF58" s="1">
+        <v>0</v>
+      </c>
       <c r="AG58" s="1">
         <v>0</v>
       </c>
@@ -3313,7 +3431,9 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
-      <c r="AF59" s="1"/>
+      <c r="AF59" s="1">
+        <v>0</v>
+      </c>
       <c r="AG59" s="1">
         <v>0</v>
       </c>
@@ -3346,7 +3466,9 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
-      <c r="AF60" s="1"/>
+      <c r="AF60" s="1">
+        <v>0</v>
+      </c>
       <c r="AG60" s="1">
         <v>0</v>
       </c>
@@ -3379,7 +3501,9 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1"/>
-      <c r="AF61" s="1"/>
+      <c r="AF61" s="1">
+        <v>0</v>
+      </c>
       <c r="AG61" s="1">
         <v>0</v>
       </c>
@@ -3413,7 +3537,9 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
-      <c r="AF62" s="1"/>
+      <c r="AF62" s="1">
+        <v>0</v>
+      </c>
       <c r="AG62" s="1">
         <v>0</v>
       </c>
@@ -3447,7 +3573,9 @@
       <c r="AC63" s="1"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
-      <c r="AF63" s="1"/>
+      <c r="AF63" s="1">
+        <v>0</v>
+      </c>
       <c r="AG63" s="1">
         <v>0</v>
       </c>
@@ -3482,7 +3610,9 @@
       <c r="AC64" s="1"/>
       <c r="AD64" s="1"/>
       <c r="AE64" s="1"/>
-      <c r="AF64" s="1"/>
+      <c r="AF64" s="1">
+        <v>0</v>
+      </c>
       <c r="AG64" s="1">
         <v>0</v>
       </c>
@@ -3517,7 +3647,9 @@
       <c r="AC65" s="1"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
-      <c r="AF65" s="1"/>
+      <c r="AF65" s="1">
+        <v>0</v>
+      </c>
       <c r="AG65" s="1">
         <v>0</v>
       </c>
@@ -3552,7 +3684,9 @@
       <c r="AC66" s="1"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
-      <c r="AF66" s="1"/>
+      <c r="AF66" s="1">
+        <v>0</v>
+      </c>
       <c r="AG66" s="1">
         <v>0</v>
       </c>
@@ -3587,7 +3721,9 @@
       <c r="AC67" s="1"/>
       <c r="AD67" s="1"/>
       <c r="AE67" s="1"/>
-      <c r="AF67" s="1"/>
+      <c r="AF67" s="1">
+        <v>0</v>
+      </c>
       <c r="AG67" s="1">
         <v>0</v>
       </c>
@@ -3610,6 +3746,10 @@
     <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>92</v>
+      </c>
+      <c r="AE68" s="1"/>
+      <c r="AF68" s="1">
+        <v>0</v>
       </c>
       <c r="AG68">
         <v>6</v>
@@ -3646,7 +3786,9 @@
       <c r="AC69" s="1"/>
       <c r="AD69" s="1"/>
       <c r="AE69" s="1"/>
-      <c r="AF69" s="1"/>
+      <c r="AF69" s="1">
+        <v>0</v>
+      </c>
       <c r="AG69" s="1">
         <v>0</v>
       </c>
@@ -3682,7 +3824,9 @@
       <c r="AC70" s="1"/>
       <c r="AD70" s="1"/>
       <c r="AE70" s="1"/>
-      <c r="AF70" s="1"/>
+      <c r="AF70" s="1">
+        <v>0</v>
+      </c>
       <c r="AG70" s="1">
         <v>0</v>
       </c>
@@ -3718,7 +3862,9 @@
       <c r="AC71" s="1"/>
       <c r="AD71" s="1"/>
       <c r="AE71" s="1"/>
-      <c r="AF71" s="1"/>
+      <c r="AF71" s="1">
+        <v>0</v>
+      </c>
       <c r="AG71" s="1">
         <v>0</v>
       </c>
@@ -3754,7 +3900,9 @@
       <c r="AC72" s="1"/>
       <c r="AD72" s="1"/>
       <c r="AE72" s="1"/>
-      <c r="AF72" s="1"/>
+      <c r="AF72" s="1">
+        <v>0</v>
+      </c>
       <c r="AG72" s="1">
         <v>0</v>
       </c>
@@ -3790,7 +3938,9 @@
       <c r="AC73" s="1"/>
       <c r="AD73" s="1"/>
       <c r="AE73" s="1"/>
-      <c r="AF73" s="1"/>
+      <c r="AF73" s="1">
+        <v>0</v>
+      </c>
       <c r="AG73" s="1">
         <v>0</v>
       </c>
@@ -3827,7 +3977,9 @@
       <c r="AC74" s="1"/>
       <c r="AD74" s="1"/>
       <c r="AE74" s="1"/>
-      <c r="AF74" s="1"/>
+      <c r="AF74" s="1">
+        <v>0</v>
+      </c>
       <c r="AG74" s="1">
         <v>0</v>
       </c>
@@ -3864,7 +4016,9 @@
       <c r="AC75" s="1"/>
       <c r="AD75" s="1"/>
       <c r="AE75" s="1"/>
-      <c r="AF75" s="1"/>
+      <c r="AF75" s="1">
+        <v>0</v>
+      </c>
       <c r="AG75" s="1">
         <v>0</v>
       </c>
@@ -3901,7 +4055,9 @@
       <c r="AC76" s="1"/>
       <c r="AD76" s="1"/>
       <c r="AE76" s="1"/>
-      <c r="AF76" s="1"/>
+      <c r="AF76" s="1">
+        <v>0</v>
+      </c>
       <c r="AG76" s="1">
         <v>0</v>
       </c>
@@ -3938,7 +4094,9 @@
       <c r="AC77" s="1"/>
       <c r="AD77" s="1"/>
       <c r="AE77" s="1"/>
-      <c r="AF77" s="1"/>
+      <c r="AF77" s="1">
+        <v>0</v>
+      </c>
       <c r="AG77" s="1">
         <v>0</v>
       </c>
@@ -3975,7 +4133,9 @@
       <c r="AC78" s="1"/>
       <c r="AD78" s="1"/>
       <c r="AE78" s="1"/>
-      <c r="AF78" s="1"/>
+      <c r="AF78" s="1">
+        <v>0</v>
+      </c>
       <c r="AG78" s="1">
         <v>0</v>
       </c>
@@ -4013,7 +4173,9 @@
       <c r="AC79" s="1"/>
       <c r="AD79" s="1"/>
       <c r="AE79" s="1"/>
-      <c r="AF79" s="1"/>
+      <c r="AF79" s="1">
+        <v>0</v>
+      </c>
       <c r="AG79" s="1">
         <v>0</v>
       </c>
@@ -4051,7 +4213,9 @@
       <c r="AC80" s="1"/>
       <c r="AD80" s="1"/>
       <c r="AE80" s="1"/>
-      <c r="AF80" s="1"/>
+      <c r="AF80" s="1">
+        <v>0</v>
+      </c>
       <c r="AG80" s="1">
         <v>0</v>
       </c>
@@ -4090,7 +4254,9 @@
       <c r="AC81" s="1"/>
       <c r="AD81" s="1"/>
       <c r="AE81" s="1"/>
-      <c r="AF81" s="1"/>
+      <c r="AF81" s="1">
+        <v>0</v>
+      </c>
       <c r="AG81" s="1">
         <v>0</v>
       </c>
@@ -4129,7 +4295,9 @@
       <c r="AC82" s="1"/>
       <c r="AD82" s="1"/>
       <c r="AE82" s="1"/>
-      <c r="AF82" s="1"/>
+      <c r="AF82" s="1">
+        <v>0</v>
+      </c>
       <c r="AG82" s="1">
         <v>0</v>
       </c>
@@ -4168,7 +4336,9 @@
       <c r="AC83" s="1"/>
       <c r="AD83" s="1"/>
       <c r="AE83" s="1"/>
-      <c r="AF83" s="1"/>
+      <c r="AF83" s="1">
+        <v>0</v>
+      </c>
       <c r="AG83" s="1">
         <v>0</v>
       </c>
@@ -4207,7 +4377,9 @@
       <c r="AC84" s="1"/>
       <c r="AD84" s="1"/>
       <c r="AE84" s="1"/>
-      <c r="AF84" s="1"/>
+      <c r="AF84" s="1">
+        <v>0</v>
+      </c>
       <c r="AG84" s="1">
         <v>0</v>
       </c>
@@ -4246,7 +4418,9 @@
       <c r="AC85" s="1"/>
       <c r="AD85" s="1"/>
       <c r="AE85" s="1"/>
-      <c r="AF85" s="1"/>
+      <c r="AF85" s="1">
+        <v>0</v>
+      </c>
       <c r="AG85" s="1">
         <v>0</v>
       </c>
@@ -4286,7 +4460,9 @@
       <c r="AC86" s="1"/>
       <c r="AD86" s="1"/>
       <c r="AE86" s="1"/>
-      <c r="AF86" s="1"/>
+      <c r="AF86" s="1">
+        <v>0</v>
+      </c>
       <c r="AG86" s="1">
         <v>0</v>
       </c>
@@ -4326,7 +4502,9 @@
       <c r="AC87" s="1"/>
       <c r="AD87" s="1"/>
       <c r="AE87" s="1"/>
-      <c r="AF87" s="1"/>
+      <c r="AF87" s="1">
+        <v>0</v>
+      </c>
       <c r="AG87" s="1">
         <v>0</v>
       </c>
@@ -4366,7 +4544,9 @@
       <c r="AC88" s="1"/>
       <c r="AD88" s="1"/>
       <c r="AE88" s="1"/>
-      <c r="AF88" s="1"/>
+      <c r="AF88" s="1">
+        <v>0</v>
+      </c>
       <c r="AG88" s="1">
         <v>0</v>
       </c>
@@ -4406,7 +4586,9 @@
       <c r="AC89" s="1"/>
       <c r="AD89" s="1"/>
       <c r="AE89" s="1"/>
-      <c r="AF89" s="1"/>
+      <c r="AF89" s="1">
+        <v>0</v>
+      </c>
       <c r="AG89" s="1">
         <v>0</v>
       </c>
@@ -4447,7 +4629,9 @@
       <c r="AC90" s="1"/>
       <c r="AD90" s="1"/>
       <c r="AE90" s="1"/>
-      <c r="AF90" s="1"/>
+      <c r="AF90" s="1">
+        <v>0</v>
+      </c>
       <c r="AG90" s="1">
         <v>0</v>
       </c>
@@ -4488,7 +4672,9 @@
       <c r="AC91" s="1"/>
       <c r="AD91" s="1"/>
       <c r="AE91" s="1"/>
-      <c r="AF91" s="1"/>
+      <c r="AF91" s="1">
+        <v>0</v>
+      </c>
       <c r="AG91" s="1">
         <v>0</v>
       </c>
@@ -4529,7 +4715,9 @@
       <c r="AC92" s="1"/>
       <c r="AD92" s="1"/>
       <c r="AE92" s="1"/>
-      <c r="AF92" s="1"/>
+      <c r="AF92" s="1">
+        <v>0</v>
+      </c>
       <c r="AG92" s="1">
         <v>0</v>
       </c>
@@ -4570,7 +4758,9 @@
       <c r="AC93" s="1"/>
       <c r="AD93" s="1"/>
       <c r="AE93" s="1"/>
-      <c r="AF93" s="1"/>
+      <c r="AF93" s="1">
+        <v>0</v>
+      </c>
       <c r="AG93" s="1">
         <v>0</v>
       </c>
@@ -4611,7 +4801,9 @@
       <c r="AC94" s="1"/>
       <c r="AD94" s="1"/>
       <c r="AE94" s="1"/>
-      <c r="AF94" s="1"/>
+      <c r="AF94" s="1">
+        <v>0</v>
+      </c>
       <c r="AG94" s="1">
         <v>0</v>
       </c>
@@ -4653,7 +4845,9 @@
       <c r="AC95" s="1"/>
       <c r="AD95" s="1"/>
       <c r="AE95" s="1"/>
-      <c r="AF95" s="1"/>
+      <c r="AF95" s="1">
+        <v>0</v>
+      </c>
       <c r="AG95" s="1">
         <v>0</v>
       </c>
@@ -4695,7 +4889,9 @@
       <c r="AC96" s="1"/>
       <c r="AD96" s="1"/>
       <c r="AE96" s="1"/>
-      <c r="AF96" s="1"/>
+      <c r="AF96" s="1">
+        <v>0</v>
+      </c>
       <c r="AG96" s="1">
         <v>0</v>
       </c>
@@ -4737,7 +4933,9 @@
       <c r="AC97" s="1"/>
       <c r="AD97" s="1"/>
       <c r="AE97" s="1"/>
-      <c r="AF97" s="1"/>
+      <c r="AF97" s="1">
+        <v>0</v>
+      </c>
       <c r="AG97" s="1">
         <v>0</v>
       </c>
@@ -4779,7 +4977,9 @@
       <c r="AC98" s="1"/>
       <c r="AD98" s="1"/>
       <c r="AE98" s="1"/>
-      <c r="AF98" s="1"/>
+      <c r="AF98" s="1">
+        <v>0</v>
+      </c>
       <c r="AG98" s="1">
         <v>0</v>
       </c>
@@ -4821,7 +5021,9 @@
       <c r="AC99" s="1"/>
       <c r="AD99" s="1"/>
       <c r="AE99" s="1"/>
-      <c r="AF99" s="1"/>
+      <c r="AF99" s="1">
+        <v>0</v>
+      </c>
       <c r="AG99" s="1">
         <v>0</v>
       </c>
@@ -4864,7 +5066,9 @@
       <c r="AC100" s="1"/>
       <c r="AD100" s="1"/>
       <c r="AE100" s="1"/>
-      <c r="AF100" s="1"/>
+      <c r="AF100" s="1">
+        <v>0</v>
+      </c>
       <c r="AG100" s="1">
         <v>0</v>
       </c>
@@ -4907,7 +5111,9 @@
       <c r="AC101" s="1"/>
       <c r="AD101" s="1"/>
       <c r="AE101" s="1"/>
-      <c r="AF101" s="1"/>
+      <c r="AF101" s="1">
+        <v>0</v>
+      </c>
       <c r="AG101" s="1">
         <v>0</v>
       </c>
@@ -4950,7 +5156,9 @@
       <c r="AC102" s="1"/>
       <c r="AD102" s="1"/>
       <c r="AE102" s="1"/>
-      <c r="AF102" s="1"/>
+      <c r="AF102" s="1">
+        <v>0</v>
+      </c>
       <c r="AG102" s="1">
         <v>0</v>
       </c>
@@ -4993,7 +5201,9 @@
       <c r="AC103" s="1"/>
       <c r="AD103" s="1"/>
       <c r="AE103" s="1"/>
-      <c r="AF103" s="1"/>
+      <c r="AF103" s="1">
+        <v>0</v>
+      </c>
       <c r="AG103" s="1">
         <v>0</v>
       </c>
@@ -5037,7 +5247,9 @@
       <c r="AC104" s="1"/>
       <c r="AD104" s="1"/>
       <c r="AE104" s="1"/>
-      <c r="AF104" s="1"/>
+      <c r="AF104" s="1">
+        <v>0</v>
+      </c>
       <c r="AG104" s="1">
         <v>0</v>
       </c>
@@ -5081,7 +5293,9 @@
       <c r="AC105" s="1"/>
       <c r="AD105" s="1"/>
       <c r="AE105" s="1"/>
-      <c r="AF105" s="1"/>
+      <c r="AF105" s="1">
+        <v>0</v>
+      </c>
       <c r="AG105" s="1">
         <v>0</v>
       </c>
@@ -5126,7 +5340,9 @@
       <c r="AC106" s="1"/>
       <c r="AD106" s="1"/>
       <c r="AE106" s="1"/>
-      <c r="AF106" s="1"/>
+      <c r="AF106" s="1">
+        <v>0</v>
+      </c>
       <c r="AG106" s="1">
         <v>0</v>
       </c>
@@ -5171,7 +5387,9 @@
       <c r="AC107" s="1"/>
       <c r="AD107" s="1"/>
       <c r="AE107" s="1"/>
-      <c r="AF107" s="1"/>
+      <c r="AF107" s="1">
+        <v>0</v>
+      </c>
       <c r="AG107" s="1">
         <v>0</v>
       </c>
@@ -5216,7 +5434,9 @@
       <c r="AC108" s="1"/>
       <c r="AD108" s="1"/>
       <c r="AE108" s="1"/>
-      <c r="AF108" s="1"/>
+      <c r="AF108" s="1">
+        <v>0</v>
+      </c>
       <c r="AG108" s="1">
         <v>0</v>
       </c>
@@ -5262,7 +5482,9 @@
       <c r="AC109" s="1"/>
       <c r="AD109" s="1"/>
       <c r="AE109" s="1"/>
-      <c r="AF109" s="1"/>
+      <c r="AF109" s="1">
+        <v>0</v>
+      </c>
       <c r="AG109" s="1">
         <v>0</v>
       </c>
@@ -5308,7 +5530,9 @@
       <c r="AC110" s="1"/>
       <c r="AD110" s="1"/>
       <c r="AE110" s="1"/>
-      <c r="AF110" s="1"/>
+      <c r="AF110" s="1">
+        <v>0</v>
+      </c>
       <c r="AG110" s="1">
         <v>0</v>
       </c>
@@ -5354,7 +5578,9 @@
       <c r="AC111" s="1"/>
       <c r="AD111" s="1"/>
       <c r="AE111" s="1"/>
-      <c r="AF111" s="1"/>
+      <c r="AF111" s="1">
+        <v>0</v>
+      </c>
       <c r="AG111" s="1">
         <v>0</v>
       </c>
@@ -5401,7 +5627,9 @@
       <c r="AC112" s="1"/>
       <c r="AD112" s="1"/>
       <c r="AE112" s="1"/>
-      <c r="AF112" s="1"/>
+      <c r="AF112" s="1">
+        <v>0</v>
+      </c>
       <c r="AG112" s="1">
         <v>0</v>
       </c>
@@ -5448,7 +5676,9 @@
       <c r="AC113" s="1"/>
       <c r="AD113" s="1"/>
       <c r="AE113" s="1"/>
-      <c r="AF113" s="1"/>
+      <c r="AF113" s="1">
+        <v>0</v>
+      </c>
       <c r="AG113" s="1">
         <v>0</v>
       </c>
@@ -5495,7 +5725,9 @@
       <c r="AC114" s="1"/>
       <c r="AD114" s="1"/>
       <c r="AE114" s="1"/>
-      <c r="AF114" s="1"/>
+      <c r="AF114" s="1">
+        <v>0</v>
+      </c>
       <c r="AG114" s="1">
         <v>0</v>
       </c>
@@ -5543,7 +5775,9 @@
       <c r="AC115" s="1"/>
       <c r="AD115" s="1"/>
       <c r="AE115" s="1"/>
-      <c r="AF115" s="1"/>
+      <c r="AF115" s="1">
+        <v>0</v>
+      </c>
       <c r="AG115" s="1">
         <v>0</v>
       </c>
@@ -5591,7 +5825,9 @@
       <c r="AC116" s="1"/>
       <c r="AD116" s="1"/>
       <c r="AE116" s="1"/>
-      <c r="AF116" s="1"/>
+      <c r="AF116" s="1">
+        <v>0</v>
+      </c>
       <c r="AG116" s="1">
         <v>0</v>
       </c>
@@ -5640,7 +5876,9 @@
       <c r="AC117" s="1"/>
       <c r="AD117" s="1"/>
       <c r="AE117" s="1"/>
-      <c r="AF117" s="1"/>
+      <c r="AF117" s="1">
+        <v>0</v>
+      </c>
       <c r="AG117" s="1">
         <v>0</v>
       </c>
@@ -5689,7 +5927,9 @@
       <c r="AC118" s="1"/>
       <c r="AD118" s="1"/>
       <c r="AE118" s="1"/>
-      <c r="AF118" s="1"/>
+      <c r="AF118" s="1">
+        <v>0</v>
+      </c>
       <c r="AG118" s="1">
         <v>0</v>
       </c>
@@ -5738,7 +5978,9 @@
       <c r="AC119" s="1"/>
       <c r="AD119" s="1"/>
       <c r="AE119" s="1"/>
-      <c r="AF119" s="1"/>
+      <c r="AF119" s="1">
+        <v>0</v>
+      </c>
       <c r="AG119" s="1">
         <v>0</v>
       </c>
@@ -5788,7 +6030,9 @@
       <c r="AC120" s="1"/>
       <c r="AD120" s="1"/>
       <c r="AE120" s="1"/>
-      <c r="AF120" s="1"/>
+      <c r="AF120" s="1">
+        <v>0</v>
+      </c>
       <c r="AG120" s="1">
         <v>0</v>
       </c>
@@ -5838,7 +6082,9 @@
       <c r="AC121" s="1"/>
       <c r="AD121" s="1"/>
       <c r="AE121" s="1"/>
-      <c r="AF121" s="1"/>
+      <c r="AF121" s="1">
+        <v>0</v>
+      </c>
       <c r="AG121" s="1">
         <v>0</v>
       </c>
@@ -5888,7 +6134,9 @@
       <c r="AC122" s="1"/>
       <c r="AD122" s="1"/>
       <c r="AE122" s="1"/>
-      <c r="AF122" s="1"/>
+      <c r="AF122" s="1">
+        <v>0</v>
+      </c>
       <c r="AG122" s="1">
         <v>0</v>
       </c>
@@ -5939,7 +6187,9 @@
       <c r="AC123" s="1"/>
       <c r="AD123" s="1"/>
       <c r="AE123" s="1"/>
-      <c r="AF123" s="1"/>
+      <c r="AF123" s="1">
+        <v>0</v>
+      </c>
       <c r="AG123" s="1">
         <v>0</v>
       </c>
@@ -5990,7 +6240,9 @@
       <c r="AC124" s="1"/>
       <c r="AD124" s="1"/>
       <c r="AE124" s="1"/>
-      <c r="AF124" s="1"/>
+      <c r="AF124" s="1">
+        <v>0</v>
+      </c>
       <c r="AG124" s="1">
         <v>0</v>
       </c>
@@ -6041,7 +6293,9 @@
       <c r="AC125" s="1"/>
       <c r="AD125" s="1"/>
       <c r="AE125" s="1"/>
-      <c r="AF125" s="1"/>
+      <c r="AF125" s="1">
+        <v>0</v>
+      </c>
       <c r="AG125" s="1">
         <v>0</v>
       </c>
@@ -6093,7 +6347,9 @@
       <c r="AC126" s="1"/>
       <c r="AD126" s="1"/>
       <c r="AE126" s="1"/>
-      <c r="AF126" s="1"/>
+      <c r="AF126" s="1">
+        <v>0</v>
+      </c>
       <c r="AG126" s="1">
         <v>0</v>
       </c>
@@ -6123,13 +6379,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12097,11 +12350,848 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>SUM(C3:S3)</f>
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f>SUM(C4:S4)</f>
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f>SUM(C5:S5)</f>
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f>SUM(C6:S6)</f>
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <f>SUM(C7:S7)</f>
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f>SUM(C8:S8)</f>
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <f>SUM(C9:S9)</f>
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <f>SUM(C10:S10)</f>
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <f>SUM(C11:S11)</f>
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <f>SUM(C12:S12)</f>
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13">
+        <f>SUM(C13:S13)</f>
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14">
+        <f>SUM(C14:S14)</f>
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
         <v>0</v>
       </c>
     </row>
